--- a/usecase/TCS_Agentic_AI_UC05_Zero_Touch_Incident_Command.xlsx
+++ b/usecase/TCS_Agentic_AI_UC05_Zero_Touch_Incident_Command.xlsx
@@ -18,18 +18,21 @@
     <sheet sheetId="12" name="12. Configuration" state="visible" r:id="rId15"/>
     <sheet sheetId="13" name="13. Verification" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="14. Implementation" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="15. Deduplication" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="16. Escalation" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="17. Change Ledger" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="775">
   <si>
     <t>UC-05 — Zero-Touch Incident Command</t>
   </si>
   <si>
-    <t>Self-detecting · Self-documenting · Self-closing incident lifecycle for OpenShift</t>
+    <t>Self-detecting · Self-documenting · Self-closing · Self-reverting incident lifecycle for OpenShift</t>
   </si>
   <si>
     <t>Attribute</t>
@@ -83,7 +86,7 @@
     <t>Relationship to UC-01</t>
   </si>
   <si>
-    <t>UC-01 answers when a human asks. UC-05 has no human trigger at all, and additionally closes its own tickets with an audit-grade RCA.</t>
+    <t>UC-01 answers when a human asks. UC-05 has no human trigger at all, closes its own tickets with an audit-grade RCA, and keeps a change ledger so every fix can be reverted.</t>
   </si>
   <si>
     <t>Demo description (short)</t>
@@ -96,7 +99,7 @@
 UC-05 removes every one of those steps except the decision to apply the fix.
 The platform continuously evaluates industry-standard thresholds against the live cluster. When a breach is sustained past its dwell time, it correlates the symptoms into a single incident, gathers real evidence (container logs — including the previous terminated instance — events, resource limits, exit codes), asks the AI for a grounded root-cause analysis, raises a properly classified ServiceNow incident into the admin queue, plans a safe remediation, and dry-runs it against the live API server.
 Then it stops and waits for one human click.
-On approval it applies the fix, verifies the workload actually recovered, and closes the ticket with a full ITIL/SRE-standard RCA attached. If the condition clears on its own first, the incident closes itself and says so. If verification fails, it escalates and deliberately leaves the ticket open rather than reporting a false success.</t>
+On approval it applies the fix, verifies the workload actually recovered, ATTACHES the RCA as HTML and PDF, links and closes duplicate tickets, closes the incident with the full RCA in the close notes, and RECORDS the change with a precomputed inverse so it can be reverted. If the condition clears on its own first, the incident closes itself and says so. If verification fails, it escalates and deliberately leaves the ticket open rather than reporting a false success.</t>
   </si>
   <si>
     <t>What makes it unique: this is not alerting and not a chatbot. Other automation stops at “alert raised” — UC-05 also writes the RCA and closes the ticket, which is the part every other tool leaves on the human.</t>
@@ -510,7 +513,7 @@
     <t>crashLoop</t>
   </si>
   <si>
-    <t>15 min · ≥3 restarts</t>
+    <t>15 min · ≥3 restarts  OR  ≥3 restarts gained in a 15-min window</t>
   </si>
   <si>
     <t>SEV-2</t>
@@ -519,7 +522,7 @@
     <t>KubePodCrashLooping</t>
   </si>
   <si>
-    <t>Container repeatedly dying — the classic outage signal</t>
+    <t>Dual trigger: state-only checks MISS a container that is Running at the instant of the scan. The mixin standard is rate-based for this reason.</t>
   </si>
   <si>
     <t>oomKilled</t>
@@ -675,13 +678,49 @@
     <t>Yes (env JSON)</t>
   </si>
   <si>
-    <t>Correlation</t>
+    <t>Causal merge</t>
+  </si>
+  <si>
+    <t>Every signal on one workload becomes ONE incident. Root cause chosen by precedence (OOM explains a crash loop, a crash loop explains zero-ready replicas); the rest are folded in as corroborating symptoms</t>
+  </si>
+  <si>
+    <t>always on</t>
+  </si>
+  <si>
+    <t>Node cascade</t>
   </si>
   <si>
     <t>A NotReady node taking N pods with it becomes 1 incident with N symptoms, not N+1 tickets</t>
   </si>
   <si>
-    <t>always on</t>
+    <t>Activity override</t>
+  </si>
+  <si>
+    <t>A chronic-by-age condition that is STILL actively restarting is treated as a live incident. Static long-standing failures stay Problem candidates</t>
+  </si>
+  <si>
+    <t>on</t>
+  </si>
+  <si>
+    <t>Yes (UI)</t>
+  </si>
+  <si>
+    <t>ServiceNow dedup</t>
+  </si>
+  <si>
+    <t>Before creating, query ServiceNow for an OPEN incident with the same correlation_id and attach to it. Holds even if our own session store was lost</t>
+  </si>
+  <si>
+    <t>Escalation</t>
+  </si>
+  <si>
+    <t>3+ recurrences raise severity one level and flag the condition for immediate attention — a returning fault is an unresolved root cause</t>
+  </si>
+  <si>
+    <t>3 episodes</t>
+  </si>
+  <si>
+    <t>Env</t>
   </si>
   <si>
     <t>Chronic guard</t>
@@ -693,9 +732,6 @@
     <t>24 hours</t>
   </si>
   <si>
-    <t>Yes (UI)</t>
-  </si>
-  <si>
     <t>Severity floor</t>
   </si>
   <si>
@@ -711,10 +747,10 @@
     <t>10 / hour</t>
   </si>
   <si>
-    <t>Signature dedup</t>
-  </si>
-  <si>
-    <t>One live incident per condition; the signature is stable across rollouts</t>
+    <t>Workload signature</t>
+  </si>
+  <si>
+    <t>The dedup key is the workload, not the rule — so it survives rollouts AND a changing mix of firing signals. No second ticket when the OOM window lapses but the crash loop continues</t>
   </si>
   <si>
     <t>Recurrence gap</t>
@@ -781,10 +817,10 @@
     <t>low</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Recreating the pods is the standard first response and is fully reversible.</t>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Recreating the pods is the standard first response. Nothing to revert — the spec was never modified.</t>
   </si>
   <si>
     <t>OOMKilled</t>
@@ -796,7 +832,10 @@
     <t>medium</t>
   </si>
   <si>
-    <t>A bare restart just repeats the kill. The limit is doubled from the observed value; if it keeps growing, profile for a leak.</t>
+    <t>YES — ledgered</t>
+  </si>
+  <si>
+    <t>A bare restart just repeats the kill. The limit is doubled from the observed value. The prior limit is captured at apply time, so this is revertable with one click.</t>
   </si>
   <si>
     <t>PVC filling up</t>
@@ -955,6 +994,33 @@
     <t>Written into the ServiceNow close notes on every incident and downloadable from the console.</t>
   </si>
   <si>
+    <t>Delivery format</t>
+  </si>
+  <si>
+    <t>Where it goes / purpose</t>
+  </si>
+  <si>
+    <t>Plain text</t>
+  </si>
+  <si>
+    <t>ServiceNow close_notes — the GUARANTEED record, always present even if attachments are blocked by policy</t>
+  </si>
+  <si>
+    <t>HTML</t>
+  </si>
+  <si>
+    <t>Attached to the incident, and served by “View RCA” in the console. Self-contained (no external CSS/fonts/images), responsive and print-ready</t>
+  </si>
+  <si>
+    <t>PDF</t>
+  </si>
+  <si>
+    <t>Attached to the incident for archival, e-mail and auditors who want a file rather than a link</t>
+  </si>
+  <si>
+    <t>Attachments are uploaded BEFORE the incident is closed — many ServiceNow configurations refuse attachments on closed records. Attachment is best-effort: a failure never costs the text record.</t>
+  </si>
+  <si>
     <t>Section</t>
   </si>
   <si>
@@ -1312,10 +1378,16 @@
     <t>30s</t>
   </si>
   <si>
+    <t>Toggle the Actionable / Chronic filter</t>
+  </si>
+  <si>
+    <t>“One actionable item, not 24 — the queue tells the truth instead of burying it.”</t>
+  </si>
+  <si>
     <t>Open ⚙ Automation Settings</t>
   </si>
   <si>
-    <t>“The autonomous switch and the ServiceNow queue are configurable here — no redeploy, no editing a Deployment.”</t>
+    <t>“The autonomous switch, the ServiceNow queue and every threshold are configurable here — no redeploy.”</t>
   </si>
   <si>
     <t>Break something live (bad image or tight memory limit)</t>
@@ -1357,13 +1429,22 @@
     <t>Click ✅ Apply Fix</t>
   </si>
   <si>
-    <t>“One click. Now it applies, verifies the pods actually recovered, and closes the ticket.”</t>
+    <t>“One click. Watch the terminal transcript and the BEFORE/AFTER container table — that is evidence, not a claim.”</t>
+  </si>
+  <si>
+    <t>45s</t>
   </si>
   <si>
     <t>Open the incident in ServiceNow</t>
   </si>
   <si>
-    <t>“Full RCA in the close notes — timeline with MTTD, MTTA, MTTR, evidence and preventive actions.”</t>
+    <t>“Full RCA in the close notes — AND the HTML and PDF reports attached to the ticket itself.”</t>
+  </si>
+  <si>
+    <t>Show History — applied changes</t>
+  </si>
+  <si>
+    <t>“Here is every change we made, with a before → after diff and a one-click revert that dry-runs first.”</t>
   </si>
   <si>
     <t>Optional: let one self-heal</t>
@@ -1372,7 +1453,7 @@
     <t>“This one fixed itself. The platform noticed and closed its own ticket.”</t>
   </si>
   <si>
-    <t>Closing line: “The only decision a human made in that entire lifecycle was whether to apply the fix.”</t>
+    <t>Closing line: “The only decision a human made in that entire lifecycle was whether to apply the fix — and even that is reversible.”</t>
   </si>
   <si>
     <t>Configuration &amp; rollout</t>
@@ -1468,6 +1549,81 @@
     <t>Consecutive clear scans before auto-closing</t>
   </si>
   <si>
+    <t>Activity beats age</t>
+  </si>
+  <si>
+    <t>INCIDENT_CHRONIC_ACTIVITY_OVERRIDE</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>A still-restarting workload is live even if it is old</t>
+  </si>
+  <si>
+    <t>Attach RCA (HTML + PDF)</t>
+  </si>
+  <si>
+    <t>INCIDENT_ATTACH_RCA / _PDF</t>
+  </si>
+  <si>
+    <t>Uploaded to the incident before it is closed</t>
+  </si>
+  <si>
+    <t>Auto-close duplicates</t>
+  </si>
+  <si>
+    <t>INCIDENT_AUTO_CLOSE_DUPLICATES</t>
+  </si>
+  <si>
+    <t>Only ever closes tickets THIS platform raised</t>
+  </si>
+  <si>
+    <t>Escalate after N recurrences</t>
+  </si>
+  <si>
+    <t>INCIDENT_ESCALATE_AFTER</t>
+  </si>
+  <si>
+    <t>Raises severity one level and flags the condition</t>
+  </si>
+  <si>
+    <t>Restart-rate window</t>
+  </si>
+  <si>
+    <t>INCIDENT_RESTART_WINDOW_MINUTES</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Window for the rate-based crashloop trigger</t>
+  </si>
+  <si>
+    <t>Change-ledger retention</t>
+  </si>
+  <si>
+    <t>CHANGE_LEDGER_RETENTION_DAYS</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>How long applied changes stay revertable in the ledger</t>
+  </si>
+  <si>
+    <t>Duplicate close code</t>
+  </si>
+  <si>
+    <t>SERVICENOW_DUPLICATE_CLOSE_CODE</t>
+  </si>
+  <si>
+    <t>Duplicate</t>
+  </si>
+  <si>
+    <t>Choice-list value varies by ServiceNow instance</t>
+  </si>
+  <si>
     <t>Scan interval</t>
   </si>
   <si>
@@ -1585,6 +1741,63 @@
     <t>VERIFIED</t>
   </si>
   <si>
+    <t>OOMKilled + CrashLoopBackOff + ZeroReadyReplicas on one workload become 1 incident with OOM as root cause</t>
+  </si>
+  <si>
+    <t>Signature stability</t>
+  </si>
+  <si>
+    <t>The signature is unchanged when the OOM window lapses and only the crash loop remains — no second ticket</t>
+  </si>
+  <si>
+    <t>Restart-rate detection</t>
+  </si>
+  <si>
+    <t>A container that is Running at scan time but gained 4 restarts IS detected (previously missed entirely)</t>
+  </si>
+  <si>
+    <t>A static 10-day failure stays chronic while a 6-day failure still restarting becomes a live incident</t>
+  </si>
+  <si>
+    <t>Fires exactly on the 3rd episode with SEV-2 → SEV-1, not on the 1st or 2nd</t>
+  </si>
+  <si>
+    <t>Duplicate asymmetry</t>
+  </si>
+  <si>
+    <t>Our duplicate is linked and closed; the human-raised ticket is linked and work-noted but never closed</t>
+  </si>
+  <si>
+    <t>Attachment degradation</t>
+  </si>
+  <si>
+    <t>An attachment failure is recorded and the close still proceeds with the text RCA intact</t>
+  </si>
+  <si>
+    <t>Ledger inverse</t>
+  </si>
+  <si>
+    <t>Correct revertable/not-revertable verdict and inverse command for all four action classes</t>
+  </si>
+  <si>
+    <t>Revert chain</t>
+  </si>
+  <si>
+    <t>The revert is recorded as its own entry and links both ways to the original, with correct stats</t>
+  </si>
+  <si>
+    <t>Native rollout undo</t>
+  </si>
+  <si>
+    <t>Restores the prior revision with the pod-template-hash stripped; refuses aged-out revisions and non-Deployments</t>
+  </si>
+  <si>
+    <t>PDF generation</t>
+  </si>
+  <si>
+    <t>Renders to a valid %PDF- buffer with all ten sections</t>
+  </si>
+  <si>
     <t>Breadth escalation</t>
   </si>
   <si>
@@ -1678,6 +1891,12 @@
     <t>PENDING LIVE</t>
   </si>
   <si>
+    <t>RCA attachment upload (live)</t>
+  </si>
+  <si>
+    <t>HTML + PDF land on the ticket in the customer instance</t>
+  </si>
+  <si>
     <t>ServiceNow auto-close (live)</t>
   </si>
   <si>
@@ -1814,13 +2033,337 @@
   </si>
   <si>
     <t>Auto-Detect tab, Approval Inbox, Automation Settings</t>
+  </si>
+  <si>
+    <t>One fault = one ticket</t>
+  </si>
+  <si>
+    <t>Three independent layers prevent duplicates, plus deliberately asymmetric handling of tickets we did not raise.</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>How it works</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>A workload that is OOMKilled AND crash-looping AND at 0/1 replicas is ONE incident. The root cause is chosen by precedence (oomKilled &gt; imagePull &gt; podPending &gt; crashLoop &gt; podNotReady &gt; zeroReady &gt; replicaMismatch) and the remaining signals are folded in as corroborating symptoms.</t>
+  </si>
+  <si>
+    <t>Per workload</t>
+  </si>
+  <si>
+    <t>The dedup key is the workload (wl:&lt;namespace&gt;:&lt;workload&gt;), not the rule. That keeps it stable across rollouts AND across a changing mix of firing signals — so no second ticket appears when the OOM window lapses but the crash loop continues.</t>
+  </si>
+  <si>
+    <t>ServiceNow correlation_id</t>
+  </si>
+  <si>
+    <t>Before creating anything we query ServiceNow for an OPEN incident carrying the same correlation_id and ATTACH to it instead. This is authoritative: it holds even when our own session store was lost to a pod restart or an unavailable database — exactly when duplicates used to slip through.</t>
+  </si>
+  <si>
+    <t>Cross-restart</t>
+  </si>
+  <si>
+    <t>When duplicates already exist</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Tickets WE raised</t>
+  </si>
+  <si>
+    <t>Linked as children of the primary (parent_incident), then closed with close_code Duplicate pointing at the primary. The full RCA lands on the primary only — duplicating nine sections across five tickets is noise.</t>
+  </si>
+  <si>
+    <t>autoCloseDuplicates (default OFF)</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Tickets a HUMAN raised</t>
+  </si>
+  <si>
+    <t>Linked and given a work note asking for review — but NEVER closed automatically. They may contain context a person added that we would destroy.</t>
+  </si>
+  <si>
+    <t>Always — no setting</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Backlog from before dedup</t>
+  </si>
+  <si>
+    <t>A reconcile sweep finds every open incident this platform raised, groups them by correlation_id, designates the oldest as primary and reports the groups. GET is read-only so the operator inspects first; POST applies.</t>
+  </si>
+  <si>
+    <t>One-click in the UI</t>
+  </si>
+  <si>
+    <t>RATIONALE: we clean up our own output automatically, but never close a person's ticket without permission. That asymmetry is what makes the automation safe to trust.</t>
+  </si>
+  <si>
+    <t>Verified call order with a stubbed ServiceNow: create primary → link ours → close ours as Duplicate → link human → work-note human → resolve primary with the RCA. The human-raised ticket is provably never closed.</t>
+  </si>
+  <si>
+    <t>Escalation — repeat offenders</t>
+  </si>
+  <si>
+    <t>A fault that keeps coming back is not another SEV-3; it is an unresolved root cause, which ITIL puts in Problem management.</t>
+  </si>
+  <si>
+    <t>Mechanism</t>
+  </si>
+  <si>
+    <t>Recurrence definition</t>
+  </si>
+  <si>
+    <t>An episode counts only when the condition CLEARED (absent from scans for longer than the recurrence gap) and then returned. A continuously-present condition stays occurrence #1 no matter how often we poll — otherwise a 2-minute poll would report 30x recurring after an hour of one flat outage.</t>
+  </si>
+  <si>
+    <t>20-minute gap</t>
+  </si>
+  <si>
+    <t>Escalation trigger</t>
+  </si>
+  <si>
+    <t>At this many episodes the detection is flagged escalated and its severity is raised one level (e.g. SEV-2 → SEV-1), which can also lift it above the auto-ticket severity floor.</t>
+  </si>
+  <si>
+    <t>Console treatment</t>
+  </si>
+  <si>
+    <t>A prominent Escalations block sits ABOVE the approval inbox and the detection list, showing each repeat offender with its occurrence count, the severity change, and direct Open Incident / Ask AI actions. Cards also carry an “escalated Nx” badge.</t>
+  </si>
+  <si>
+    <t>Recommended response</t>
+  </si>
+  <si>
+    <t>Raise a Problem record rather than closing another Incident. The RCA already carries a CAPA section, and recurrence is called out there explicitly.</t>
+  </si>
+  <si>
+    <t>guidance</t>
+  </si>
+  <si>
+    <t>Activity override (related)</t>
+  </si>
+  <si>
+    <t>Separately, a condition that is chronic BY AGE but still actively restarting is reclassified as a live incident — churning is not the same as stale.</t>
+  </si>
+  <si>
+    <t>Episode</t>
+  </si>
+  <si>
+    <t>Occurrences</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>1st</t>
+  </si>
+  <si>
+    <t>SEV-2 — normal handling</t>
+  </si>
+  <si>
+    <t>2nd</t>
+  </si>
+  <si>
+    <t>3rd</t>
+  </si>
+  <si>
+    <t>ESCALATED → SEV-1, flagged for immediate attention</t>
+  </si>
+  <si>
+    <t>4th+</t>
+  </si>
+  <si>
+    <t>4+</t>
+  </si>
+  <si>
+    <t>Remains escalated; escalation level increases with each multiple of the threshold</t>
+  </si>
+  <si>
+    <t>Verified: escalation triggers exactly on the 3rd episode with SEV-2 → SEV-1, and does not fire on the 1st or 2nd.</t>
+  </si>
+  <si>
+    <t>Change Ledger &amp; Revert</t>
+  </si>
+  <si>
+    <t>Every mutation the automation applied, with a precomputed inverse — surfaced as “History — applied changes” once an incident is fixed.</t>
+  </si>
+  <si>
+    <t>THE KEY DESIGN DECISION: the inverse is computed and stored AT APPLY TIME, not at revert time. Once memory has been patched from 389Mi to 778Mi the old value is gone from the live object — it can only be restored if it was captured beforehand.</t>
+  </si>
+  <si>
+    <t>Revertable?</t>
+  </si>
+  <si>
+    <t>increase_memory</t>
+  </si>
+  <si>
+    <t>YES — exact inverse patch</t>
+  </si>
+  <si>
+    <t>The prior limit and container name are captured while the fix is planned, so the exact inverse command can be built and stored.</t>
+  </si>
+  <si>
+    <t>rollout_restart</t>
+  </si>
+  <si>
+    <t>No — nothing to revert</t>
+  </si>
+  <si>
+    <t>A rolling restart changes no configuration; only the pods were recreated. A revert button here would be meaningless.</t>
+  </si>
+  <si>
+    <t>expand_pvc</t>
+  </si>
+  <si>
+    <t>No — physically impossible</t>
+  </si>
+  <si>
+    <t>Kubernetes cannot shrink a PersistentVolumeClaim. Expansion is one-way; reducing capacity means migrating the data to a smaller volume.</t>
+  </si>
+  <si>
+    <t>(no captured value)</t>
+  </si>
+  <si>
+    <t>Native rollout undo offered</t>
+  </si>
+  <si>
+    <t>Falls back to `oc rollout undo`, which restores the entire prior pod template from the retained ReplicaSet revision.</t>
+  </si>
+  <si>
+    <t>Field recorded</t>
+  </si>
+  <si>
+    <t>what / where</t>
+  </si>
+  <si>
+    <t>Identify the target</t>
+  </si>
+  <si>
+    <t>cluster, namespace, resource kind, resource name, container</t>
+  </si>
+  <si>
+    <t>action + command</t>
+  </si>
+  <si>
+    <t>What ran</t>
+  </si>
+  <si>
+    <t>The exact command that was applied</t>
+  </si>
+  <si>
+    <t>beforeValue / afterValue</t>
+  </si>
+  <si>
+    <t>The diff</t>
+  </si>
+  <si>
+    <t>e.g. containers.mlflow.limits.memory: 389Mi → 778Mi — rendered as a red/green diff in the UI</t>
+  </si>
+  <si>
+    <t>revertCommand</t>
+  </si>
+  <si>
+    <t>The undo</t>
+  </si>
+  <si>
+    <t>Precomputed inverse, stored at apply time</t>
+  </si>
+  <si>
+    <t>nativeUndo</t>
+  </si>
+  <si>
+    <t>Fallback undo</t>
+  </si>
+  <si>
+    <t>The equivalent `oc rollout undo` command</t>
+  </si>
+  <si>
+    <t>revertable + revertReason</t>
+  </si>
+  <si>
+    <t>Honesty</t>
+  </si>
+  <si>
+    <t>When it cannot be reverted, the reason is shown instead of a button that would lie</t>
+  </si>
+  <si>
+    <t>provenance</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>sessionId, signature, incident number, who approved it, timestamps</t>
+  </si>
+  <si>
+    <t>evidence</t>
+  </si>
+  <si>
+    <t>Proof</t>
+  </si>
+  <si>
+    <t>dry-run output, apply output, verification result, before/after container snapshots</t>
+  </si>
+  <si>
+    <t>revertOf</t>
+  </si>
+  <si>
+    <t>The chain</t>
+  </si>
+  <si>
+    <t>Set when this entry IS a revert — so the ledger is a complete chain and a revert can itself be reverted</t>
+  </si>
+  <si>
+    <t>Revert governance</t>
+  </si>
+  <si>
+    <t>The revert command is risk-classified before anything runs; blocked commands never reach the cluster.</t>
+  </si>
+  <si>
+    <t>A dry-run is ALWAYS executed first, even when the caller asked to apply — an unverified revert turns one incident into two.</t>
+  </si>
+  <si>
+    <t>Verification</t>
+  </si>
+  <si>
+    <t>The same workload health check used for a fix confirms the revert actually took effect.</t>
+  </si>
+  <si>
+    <t>Incident work note</t>
+  </si>
+  <si>
+    <t>A work note is posted to the originating incident (usually already closed) so the audit trail stays followable.</t>
+  </si>
+  <si>
+    <t>openshift-*, kube-*, default are refused — revert those manually.</t>
+  </si>
+  <si>
+    <t>Every revert is written to the audit log with the actor, command and verification outcome.</t>
+  </si>
+  <si>
+    <t>WHY NOT ALWAYS `oc rollout undo`? Undo restores the ENTIRE prior pod template and would silently discard any unrelated change someone made since. The inverse patch undoes exactly what we did and nothing else. Native undo (and `rollout history`) are both implemented and available where no before-value was captured.</t>
+  </si>
+  <si>
+    <t>Verified: inverse computation for all four action classes; the ledger records and the revert chain links both ways with correct stats; `rollout undo` restores the prior revision with the controller-managed pod-template-hash stripped, and correctly refuses aged-out revisions and non-Deployment kinds. Caveat: without PostgreSQL the ledger is in-memory and lost on pod restart.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1892,8 +2435,14 @@
       <sz val="10.5"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF5B21B6"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1950,6 +2499,11 @@
         <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE9FE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1978,7 +2532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -2017,6 +2571,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -2499,7 +3056,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2507,7 +3064,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2515,86 +3072,86 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2602,46 +3159,46 @@
         <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -2663,7 +3220,7 @@
   <sheetPr>
     <tabColor rgb="FFD97706"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2674,7 +3231,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2682,7 +3239,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2693,13 +3250,13 @@
         <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2707,13 +3264,13 @@
         <v>31</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2721,13 +3278,13 @@
         <v>36</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2735,13 +3292,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -2749,126 +3306,154 @@
         <v>42</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>423</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>423</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="B16" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+    </row>
+    <row r="19" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2880,7 +3465,7 @@
   <sheetPr>
     <tabColor rgb="FF64748B"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2892,7 +3477,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2901,7 +3486,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2910,307 +3495,426 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>209</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>161</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>121</v>
+        <v>483</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>229</v>
+        <v>509</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>486</v>
+        <v>512</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>488</v>
-      </c>
       <c r="D14" s="7" t="s">
-        <v>121</v>
+        <v>483</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>489</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>490</v>
+        <v>515</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>491</v>
+        <v>516</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>461</v>
+        <v>39</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>121</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="D17" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="D18" s="5" t="s">
+    <row r="25" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="D19" s="7" t="s">
+    <row r="26" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E26" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="D20" s="5" t="s">
+    <row r="27" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="D21" s="7" t="s">
+    <row r="28" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E28" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="D22" s="5" t="s">
+    <row r="29" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3229,7 +3933,7 @@
   <sheetPr>
     <tabColor rgb="FF0891B2"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -3239,250 +3943,382 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>510</v>
+        <v>561</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>511</v>
+        <v>562</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>512</v>
+        <v>563</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>513</v>
+        <v>564</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>514</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>515</v>
+        <v>566</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>516</v>
+        <v>567</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>518</v>
+        <v>215</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>519</v>
+        <v>569</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>520</v>
+        <v>570</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>521</v>
+        <v>571</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>522</v>
+        <v>572</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>523</v>
+        <v>573</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>524</v>
+        <v>574</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>525</v>
+        <v>226</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>526</v>
+        <v>575</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>527</v>
+        <v>576</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>528</v>
+        <v>577</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>529</v>
+        <v>578</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>530</v>
+        <v>579</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>531</v>
+        <v>580</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>532</v>
+        <v>581</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>533</v>
+        <v>582</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>534</v>
+        <v>583</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>535</v>
+        <v>584</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>536</v>
+        <v>585</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>233</v>
+        <v>586</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>537</v>
+        <v>587</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>538</v>
+        <v>588</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>539</v>
+        <v>589</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>540</v>
+        <v>590</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>541</v>
+        <v>591</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>542</v>
+        <v>592</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>543</v>
+        <v>593</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>544</v>
+        <v>230</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>545</v>
+        <v>594</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>517</v>
+        <v>568</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>546</v>
+        <v>595</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>547</v>
+        <v>596</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>549</v>
+        <v>597</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>550</v>
+        <v>598</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>551</v>
+        <v>599</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>552</v>
+        <v>600</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>553</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
+        <v>568</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
+        <v>625</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A37:C37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3503,165 +4339,804 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>554</v>
+        <v>626</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>555</v>
+        <v>627</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>556</v>
+        <v>628</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>557</v>
+        <v>629</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>558</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>559</v>
+        <v>631</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>560</v>
+        <v>632</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>561</v>
+        <v>633</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>562</v>
+        <v>634</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>563</v>
+        <v>635</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>564</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>565</v>
+        <v>637</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>566</v>
+        <v>638</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>567</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>568</v>
+        <v>640</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>569</v>
+        <v>641</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>570</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>571</v>
+        <v>643</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>572</v>
+        <v>644</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>573</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>574</v>
+        <v>646</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>575</v>
+        <v>647</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>576</v>
+        <v>648</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>577</v>
+        <v>649</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>578</v>
+        <v>650</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>579</v>
+        <v>651</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>581</v>
+        <v>653</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>582</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>583</v>
+        <v>655</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>584</v>
+        <v>656</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>585</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>586</v>
+        <v>658</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>587</v>
+        <v>659</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>588</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>589</v>
+        <v>661</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>590</v>
+        <v>662</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>591</v>
+        <v>663</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>592</v>
+        <v>664</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>593</v>
+        <v>665</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>594</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF0891B2"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="74" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>680</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+    </row>
+    <row r="16" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A16:D16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFDC2626"/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="78" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A17:C17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFEA580C"/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="72" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+    </row>
+    <row r="6" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>731</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>753</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>770</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>773</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+    </row>
+    <row r="33" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>774</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A33:C33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4646,7 +6121,7 @@
   <sheetPr>
     <tabColor rgb="FF059669"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -4721,24 +6196,24 @@
         <v>219</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4749,38 +6224,38 @@
         <v>225</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>221</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>217</v>
-      </c>
       <c r="D10" s="7" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4791,10 +6266,10 @@
         <v>234</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>33</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4808,31 +6283,87 @@
         <v>237</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="B14" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="C14" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="21" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A21:D21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4856,7 +6387,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4865,7 +6396,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4874,78 +6405,78 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>33</v>
@@ -4954,15 +6485,15 @@
         <v>33</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>33</v>
@@ -4971,15 +6502,15 @@
         <v>33</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>33</v>
@@ -4988,15 +6519,15 @@
         <v>33</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>33</v>
@@ -5005,12 +6536,12 @@
         <v>33</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -5042,19 +6573,19 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -5062,135 +6593,135 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B23" s="10"/>
     </row>
@@ -5210,7 +6741,7 @@
   <sheetPr>
     <tabColor rgb="FF0891B2"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -5219,187 +6750,226 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B9" s="10"/>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>325</v>
+      <c r="A12" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>327</v>
+      <c r="A13" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>329</v>
+      <c r="A14" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>278</v>
+      <c r="A15" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>332</v>
+      <c r="A16" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>334</v>
+      <c r="A17" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>336</v>
+      <c r="A18" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>338</v>
+      <c r="A19" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>340</v>
+      <c r="A20" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>342</v>
+      <c r="A21" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>344</v>
+      <c r="A22" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="B25" s="9"/>
+      <c r="A23" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="B32" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A32:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5421,21 +6991,21 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>87</v>
@@ -5446,139 +7016,139 @@
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>

--- a/usecase/TCS_Agentic_AI_UC05_Zero_Touch_Incident_Command.xlsx
+++ b/usecase/TCS_Agentic_AI_UC05_Zero_Touch_Incident_Command.xlsx
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="775">
-  <si>
-    <t>UC-05 — Zero-Touch Incident Command</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="779">
+  <si>
+    <t>TCS Agentic AI — Zero-Touch Incident Command  (ZTIC)  ·  UC-05</t>
   </si>
   <si>
     <t>Self-detecting · Self-documenting · Self-closing · Self-reverting incident lifecycle for OpenShift</t>
@@ -47,10 +47,22 @@
     <t>UC-05</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Zero-Touch Incident Command</t>
+    <t>Full name</t>
+  </si>
+  <si>
+    <t>TCS Agentic AI — Zero-Touch Incident Command</t>
+  </si>
+  <si>
+    <t>Short name (use in demos)</t>
+  </si>
+  <si>
+    <t>ZTIC</t>
+  </si>
+  <si>
+    <t>Product family</t>
+  </si>
+  <si>
+    <t>TCS Agentic AI for OpenShift · Tata Consultancy Services</t>
   </si>
   <si>
     <t>Tagline</t>
@@ -105,7 +117,7 @@
     <t>What makes it unique: this is not alerting and not a chatbot. Other automation stops at “alert raised” — UC-05 also writes the RCA and closes the ticket, which is the part every other tool leaves on the human.</t>
   </si>
   <si>
-    <t>UC-05 Workflow — step by step</t>
+    <t>TCS Agentic AI · ZTIC — Workflow, step by step</t>
   </si>
   <si>
     <t>Everything before the approval gate is autonomous. Everything after it is autonomous.</t>
@@ -375,7 +387,7 @@
     <t>ASCII flow:  Detect → Dwell → Correlate → Fingerprint → Eligibility → Triage(AI RCA) → Raise INC → Plan fix → Dry-run → [ APPROVAL ] → Apply → Verify → Resolve → Close+RCA</t>
   </si>
   <si>
-    <t>Lifecycle state machine — 15 states</t>
+    <t>TCS Agentic AI · ZTIC — Lifecycle state machine (15 states)</t>
   </si>
   <si>
     <t>Transitions are enforced; an invalid transition is rejected rather than silently applied.</t>
@@ -489,7 +501,7 @@
     <t>Only AWAITING_APPROVAL requires a person. Every other transition is driven by the platform.</t>
   </si>
   <si>
-    <t>Detection thresholds — global industry standard</t>
+    <t>TCS Agentic AI · ZTIC — Detection thresholds (global industry standard)</t>
   </si>
   <si>
     <t>Defaults come from the kubernetes-mixin / kube-prometheus rules OpenShift already ships. Dwell time is the equivalent of a Prometheus rule's `for:` clause.</t>
@@ -648,7 +660,7 @@
     <t>All thresholds are overridable per customer via INCIDENT_THRESHOLDS (JSON) without a code change.</t>
   </si>
   <si>
-    <t>Noise control — what makes autonomy credible</t>
+    <t>TCS Agentic AI · ZTIC — Noise control: what makes autonomy credible</t>
   </si>
   <si>
     <t>Without these guards, enabling auto-ticketing on a real cluster creates an alert storm on the very first scan.</t>
@@ -786,7 +798,7 @@
     <t>Without the chronic guard this cluster would have opened 24 tickets on the first scan — the difference between a demo that lands and one that doesn't.</t>
   </si>
   <si>
-    <t>Remediation catalogue — one safe action per signal</t>
+    <t>TCS Agentic AI · ZTIC — Remediation catalogue (one safe action per signal)</t>
   </si>
   <si>
     <t>Anything not listed escalates with the RCA and ticket already prepared. The system never guesses at a fix.</t>
@@ -880,7 +892,7 @@
     <t>Every action is guardrail-classified, dry-run against the live API server, and applied only after explicit human approval.</t>
   </si>
   <si>
-    <t>AI root-cause analysis — evidence-grounded</t>
+    <t>TCS Agentic AI · ZTIC — AI root-cause analysis (evidence-grounded)</t>
   </si>
   <si>
     <t>Logs and events are attacker-influencable, so they are fenced as untrusted data — the model treats them as evidence, never as instructions.</t>
@@ -988,7 +1000,7 @@
     <t>Bounded: 35s AI / 20s evidence soft timeouts. If the LLM is slow or not configured, the RCA still renders from the deterministic engine and states that explicitly — it never silently degrades.</t>
   </si>
   <si>
-    <t>RCA document structure — ITIL 4 · Google SRE · NIST SP 800-61</t>
+    <t>TCS Agentic AI · ZTIC — RCA document (ITIL 4 · Google SRE · NIST SP 800-61)</t>
   </si>
   <si>
     <t>Written into the ServiceNow close notes on every incident and downloadable from the console.</t>
@@ -1141,7 +1153,7 @@
     <t>Every incident closes with the same audit-grade document, regardless of who was on call — which is what auditors actually ask for.</t>
   </si>
   <si>
-    <t>Safety model</t>
+    <t>TCS Agentic AI · ZTIC — Safety model</t>
   </si>
   <si>
     <t>Autonomy is only acceptable if it is bounded, previewed, verified and auditable.</t>
@@ -1231,7 +1243,7 @@
     <t>NEVER A FALSE SUCCESS: an unverified fix escalates and leaves the ticket open. The system would rather admit uncertainty than close a ticket it cannot justify.</t>
   </si>
   <si>
-    <t>Business value — where the time goes back</t>
+    <t>TCS Agentic AI · ZTIC — Business value: where the time goes back</t>
   </si>
   <si>
     <t>The target is the administrative load, not the engineering judgement.</t>
@@ -1345,7 +1357,7 @@
     <t>THE DIFFERENTIATOR: other automation stops at “alert raised”. UC-05 also writes the RCA and closes the ticket — the part every other tool leaves on the human.</t>
   </si>
   <si>
-    <t>Demo script — five minutes</t>
+    <t>TCS Agentic AI · ZTIC — Demo script</t>
   </si>
   <si>
     <t>Run in shadow mode first, then enable autonomous action for the live portion.</t>
@@ -1456,7 +1468,7 @@
     <t>Closing line: “The only decision a human made in that entire lifecycle was whether to apply the fix — and even that is reversible.”</t>
   </si>
   <si>
-    <t>Configuration &amp; rollout</t>
+    <t>TCS Agentic AI · ZTIC — Configuration &amp; rollout</t>
   </si>
   <si>
     <t>Everything an operator needs to tune is editable in the UI and persisted — no pod restart.</t>
@@ -1717,7 +1729,7 @@
     <t>Validates the ServiceNow integration against the live instance</t>
   </si>
   <si>
-    <t>Verification status</t>
+    <t>TCS Agentic AI · ZTIC — Verification status</t>
   </si>
   <si>
     <t>Honest separation between what has been proven and what still needs live validation.</t>
@@ -1912,7 +1924,7 @@
     <t>Verified items were exercised with automated harnesses against synthetic clusters matching the live cluster's shape. Items marked PENDING LIVE require the customer's ServiceNow instance and LLM endpoint.</t>
   </si>
   <si>
-    <t>Implementation map</t>
+    <t>TCS Agentic AI · ZTIC — Implementation map</t>
   </si>
   <si>
     <t>Where each capability lives in the codebase.</t>
@@ -2035,7 +2047,7 @@
     <t>Auto-Detect tab, Approval Inbox, Automation Settings</t>
   </si>
   <si>
-    <t>One fault = one ticket</t>
+    <t>TCS Agentic AI · ZTIC — One fault = one ticket</t>
   </si>
   <si>
     <t>Three independent layers prevent duplicates, plus deliberately asymmetric handling of tickets we did not raise.</t>
@@ -2113,7 +2125,7 @@
     <t>Verified call order with a stubbed ServiceNow: create primary → link ours → close ours as Duplicate → link human → work-note human → resolve primary with the RCA. The human-raised ticket is provably never closed.</t>
   </si>
   <si>
-    <t>Escalation — repeat offenders</t>
+    <t>TCS Agentic AI · ZTIC — Escalation: repeat offenders</t>
   </si>
   <si>
     <t>A fault that keeps coming back is not another SEV-3; it is an unresolved root cause, which ITIL puts in Problem management.</t>
@@ -2194,7 +2206,7 @@
     <t>Verified: escalation triggers exactly on the 3rd episode with SEV-2 → SEV-1, and does not fire on the 1st or 2nd.</t>
   </si>
   <si>
-    <t>Change Ledger &amp; Revert</t>
+    <t>TCS Agentic AI · ZTIC — Change Ledger &amp; Revert</t>
   </si>
   <si>
     <t>Every mutation the automation applied, with a precomputed inverse — surfaced as “History — applied changes” once an incident is fixed.</t>
@@ -2918,7 +2930,7 @@
   <sheetPr>
     <tabColor rgb="FF2563EB"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3009,32 +3021,48 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="13" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" ht="210" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+    <row r="14" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="8"/>
-    </row>
-    <row r="17" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="9"/>
+    </row>
+    <row r="16" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" ht="210" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="8"/>
+    </row>
+    <row r="19" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3056,7 +3084,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3064,7 +3092,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3072,133 +3100,133 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -3231,7 +3259,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3239,7 +3267,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3247,203 +3275,203 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>448</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>451</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -3477,7 +3505,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3486,7 +3514,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3495,427 +3523,427 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>483</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>483</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3943,373 +3971,373 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>572</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>622</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="37" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -4339,159 +4367,159 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -4520,7 +4548,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4528,7 +4556,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4536,119 +4564,119 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="6" ht="62" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="7" ht="62" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -4656,7 +4684,7 @@
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -4689,142 +4717,142 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -4855,86 +4883,86 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>3</v>
@@ -4942,190 +4970,190 @@
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -5160,7 +5188,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5169,7 +5197,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5178,381 +5206,381 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="24" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -5586,7 +5614,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5594,7 +5622,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5602,231 +5630,231 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -5859,7 +5887,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5868,7 +5896,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5877,228 +5905,228 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>161</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>174</v>
-      </c>
       <c r="C9" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -6132,7 +6160,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6140,7 +6168,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6148,203 +6176,203 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -6352,7 +6380,7 @@
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -6387,7 +6415,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6396,7 +6424,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6405,143 +6433,143 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>265</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>273</v>
-      </c>
       <c r="C10" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -6573,19 +6601,19 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -6593,135 +6621,135 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B23" s="10"/>
     </row>
@@ -6750,217 +6778,217 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B9" s="10"/>
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B32" s="9"/>
     </row>
@@ -6991,164 +7019,164 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>384</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>

--- a/usecase/TCS_Agentic_AI_UC05_Zero_Touch_Incident_Command.xlsx
+++ b/usecase/TCS_Agentic_AI_UC05_Zero_Touch_Incident_Command.xlsx
@@ -21,13 +21,14 @@
     <sheet sheetId="15" name="15. Deduplication" state="visible" r:id="rId18"/>
     <sheet sheetId="16" name="16. Escalation" state="visible" r:id="rId19"/>
     <sheet sheetId="17" name="17. Change Ledger" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="18. Actor Matrix" state="visible" r:id="rId21"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="856">
   <si>
     <t>TCS Agentic AI — Zero-Touch Incident Command  (ZTIC)  ·  UC-05</t>
   </si>
@@ -150,7 +151,7 @@
     <t>Background loop (every 2 min) evaluates 12 industry-standard thresholds against pods, nodes, deployments, cluster operators, PVCs and Alertmanager.</t>
   </si>
   <si>
-    <t>AI · automatic</t>
+    <t>AUTOMATIC</t>
   </si>
   <si>
     <t>2</t>
@@ -201,7 +202,19 @@
     <t>TRIAGED</t>
   </si>
   <si>
-    <t>Gather evidence (container logs incl. previous terminated instance, warning events, resource limits, exit codes) and run AI root-cause analysis.</t>
+    <t>Gather evidence: container logs including the PREVIOUS terminated instance, warning events, resource limits, exit codes.</t>
+  </si>
+  <si>
+    <t>6b</t>
+  </si>
+  <si>
+    <t>AI analysis</t>
+  </si>
+  <si>
+    <t>The one AI step. An LLM reasons over that evidence to produce the root-cause narrative, category, confidence, 5-Whys chain, contributing factors and preventive actions. It EXPLAINS — it never chooses or executes a command.</t>
+  </si>
+  <si>
+    <t>AI (LLM)</t>
   </si>
   <si>
     <t>7</t>
@@ -225,7 +238,7 @@
     <t>FIX_PROPOSED</t>
   </si>
   <si>
-    <t>Deterministic remediation planner selects ONE safe action for the signal class; the command is classified by guardrails.</t>
+    <t>A DETERMINISTIC table selects ONE safe action for the signal class — deliberately not the AI — then guardrails classify the command.</t>
   </si>
   <si>
     <t>9</t>
@@ -252,7 +265,7 @@
     <t>The ONLY human step. Operator reviews the RCA and the dry-run output, then clicks Apply Fix (or Reject).</t>
   </si>
   <si>
-    <t>HUMAN</t>
+    <t>MANUAL</t>
   </si>
   <si>
     <t>11</t>
@@ -2369,6 +2382,225 @@
   </si>
   <si>
     <t>Verified: inverse computation for all four action classes; the ledger records and the revert chain links both ways with correct stats; `rollout undo` restores the prior revision with the controller-managed pod-template-hash stripped, and correctly refuses aged-out revisions and non-Deployment kinds. Caveat: without PostgreSQL the ledger is in-memory and lost on pod restart.</t>
+  </si>
+  <si>
+    <t>TCS Agentic AI · ZTIC — Who does what: AI, automatic, or manual</t>
+  </si>
+  <si>
+    <t>The AI explains. Deterministic code acts. A human decides. Being precise about this is more reassuring to an operator than claiming AI does everything.</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>What it means and where it is used</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>AI (LLM reasoning)</t>
+  </si>
+  <si>
+    <t>1 step</t>
+  </si>
+  <si>
+    <t>Reasons over the gathered evidence to produce the root-cause narrative, category, confidence rating, 5-Whys causal chain, contributing factors, impact assessment, investigation steps and preventive actions. It EXPLAINS — it never selects or executes a command.</t>
+  </si>
+  <si>
+    <t>AUTO</t>
+  </si>
+  <si>
+    <t>AUTOMATIC (deterministic)</t>
+  </si>
+  <si>
+    <t>20 steps</t>
+  </si>
+  <si>
+    <t>Plain code with no AI and no human: detection, dwell evaluation, correlation and causal merge, fingerprinting, eligibility policy, evidence gathering, duplicate lookup, ticket raise/reuse, remediation planning, guardrail classification, dry-run, apply, verification, RCA attachment, duplicate closure, incident closure, ledger recording, self-heal closure, external-closure reconciliation.</t>
+  </si>
+  <si>
+    <t>MANUAL (a person)</t>
+  </si>
+  <si>
+    <t>1 decision</t>
+  </si>
+  <si>
+    <t>Approving or rejecting the proposed fix. Optionally: reverting a change, tuning thresholds and settings, and owning an escalation when no safe automated fix exists.</t>
+  </si>
+  <si>
+    <t>KEY DESIGN POINT: the remediation command is chosen by a DETERMINISTIC table, not by the AI. A language model writes the explanation; fixed rules decide what is actually executed against the cluster. The AI can therefore be wrong about “why” without ever being able to run the wrong command.</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Scan cluster + Alertmanager</t>
+  </si>
+  <si>
+    <t>Read-only API calls, every 2 minutes</t>
+  </si>
+  <si>
+    <t>Threshold + dwell evaluation</t>
+  </si>
+  <si>
+    <t>kubernetes-mixin / kube-prometheus rule values</t>
+  </si>
+  <si>
+    <t>Correlation / causal merge</t>
+  </si>
+  <si>
+    <t>Precedence table picks the root-cause signal — not AI</t>
+  </si>
+  <si>
+    <t>Fingerprint · chronic · recurrence · escalation</t>
+  </si>
+  <si>
+    <t>Deterministic classification</t>
+  </si>
+  <si>
+    <t>Eligibility (severity floor, rate limit)</t>
+  </si>
+  <si>
+    <t>Policy check</t>
+  </si>
+  <si>
+    <t>Gather evidence</t>
+  </si>
+  <si>
+    <t>Logs incl. the previous terminated container, events, limits, exit codes</t>
+  </si>
+  <si>
+    <t>ROOT-CAUSE ANALYSIS</t>
+  </si>
+  <si>
+    <t>THE ONE AI STEP — narrative, category, confidence, 5-Whys, CAPA</t>
+  </si>
+  <si>
+    <t>Deterministic RCA fallback</t>
+  </si>
+  <si>
+    <t>Used when the LLM is slow or not configured; the RCA still renders</t>
+  </si>
+  <si>
+    <t>Known-error knowledge-base match</t>
+  </si>
+  <si>
+    <t>Regex catalogue matched against the real logs and events</t>
+  </si>
+  <si>
+    <t>Duplicate check via correlation_id</t>
+  </si>
+  <si>
+    <t>ServiceNow is the source of truth</t>
+  </si>
+  <si>
+    <t>Raise or reuse the incident</t>
+  </si>
+  <si>
+    <t>ITIL Impact × Urgency matrix, admin assignment group</t>
+  </si>
+  <si>
+    <t>PLAN THE REMEDIATION</t>
+  </si>
+  <si>
+    <t>DELIBERATELY NOT AI — a fixed table, one safe action per signal class</t>
+  </si>
+  <si>
+    <t>Guardrail risk classification</t>
+  </si>
+  <si>
+    <t>Blocked commands never reach the cluster</t>
+  </si>
+  <si>
+    <t>?dryRun=All against the live API server</t>
+  </si>
+  <si>
+    <t>APPROVE OR REJECT</t>
+  </si>
+  <si>
+    <t>THE ONLY REQUIRED HUMAN STEP</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Apply the fix</t>
+  </si>
+  <si>
+    <t>Container snapshot captured first</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Verify workload health</t>
+  </si>
+  <si>
+    <t>Polls until healthy or the attempt budget is spent</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Uploaded before the incident is closed</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Link + close duplicate tickets</t>
+  </si>
+  <si>
+    <t>Human-raised tickets are linked and annotated but never closed</t>
+  </si>
+  <si>
+    <t>Close the incident with the RCA</t>
+  </si>
+  <si>
+    <t>Full RCA in the close notes</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Record in the Change Ledger</t>
+  </si>
+  <si>
+    <t>With the precomputed inverse for revert</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Self-heal closure</t>
+  </si>
+  <si>
+    <t>Condition cleared on its own — no human, no fix applied</t>
+  </si>
+  <si>
+    <t>Revert a change</t>
+  </si>
+  <si>
+    <t>MANUAL (optional)</t>
+  </si>
+  <si>
+    <t>Dry-run → apply → verify, the same governance as the original fix</t>
+  </si>
+  <si>
+    <t>Tune thresholds / settings</t>
+  </si>
+  <si>
+    <t>Editable in the UI, applied live without a restart</t>
+  </si>
+  <si>
+    <t>Own an escalation</t>
+  </si>
+  <si>
+    <t>When no safe automated fix exists, or verification failed</t>
+  </si>
+  <si>
+    <t>TOTALS: 20 automatic · 1 AI · 1 required human decision. Exception paths hand back to a human with the RCA and ticket already prepared.</t>
   </si>
 </sst>
 </file>
@@ -3084,7 +3316,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3092,7 +3324,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3100,86 +3332,86 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3187,46 +3419,46 @@
         <v>16</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -3259,7 +3491,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3267,7 +3499,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3278,13 +3510,13 @@
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3292,13 +3524,13 @@
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3306,13 +3538,13 @@
         <v>40</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3320,13 +3552,13 @@
         <v>43</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>452</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3334,13 +3566,13 @@
         <v>46</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>455</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3348,13 +3580,13 @@
         <v>46</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3362,13 +3594,13 @@
         <v>50</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3376,102 +3608,102 @@
         <v>53</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -3505,7 +3737,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3514,7 +3746,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3523,336 +3755,336 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>487</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>487</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
@@ -3863,13 +4095,13 @@
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>25</v>
@@ -3880,13 +4112,13 @@
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>25</v>
@@ -3897,13 +4129,13 @@
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>25</v>
@@ -3914,13 +4146,13 @@
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>25</v>
@@ -3931,13 +4163,13 @@
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>25</v>
@@ -3971,373 +4203,373 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>576</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>577</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>626</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="37" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
@@ -4367,159 +4599,159 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -4548,7 +4780,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4556,7 +4788,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4567,13 +4799,13 @@
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4581,13 +4813,13 @@
         <v>35</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" ht="62" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4595,13 +4827,13 @@
         <v>40</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7" ht="62" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4609,13 +4841,13 @@
         <v>43</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -4623,60 +4855,60 @@
         <v>25</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -4684,7 +4916,7 @@
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -4717,142 +4949,142 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -4883,86 +5115,86 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>3</v>
@@ -4970,109 +5202,109 @@
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>25</v>
@@ -5080,10 +5312,10 @@
     </row>
     <row r="24" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>25</v>
@@ -5091,10 +5323,10 @@
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>25</v>
@@ -5102,10 +5334,10 @@
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>25</v>
@@ -5113,10 +5345,10 @@
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>25</v>
@@ -5124,10 +5356,10 @@
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>25</v>
@@ -5135,10 +5367,10 @@
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>25</v>
@@ -5146,14 +5378,14 @@
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -5171,12 +5403,490 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF7C3AED"/>
+  </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="66" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>798</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+    </row>
+    <row r="11" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A38:D38"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF7C3AED"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5331,13 +6041,13 @@
         <v>58</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5388,24 +6098,24 @@
         <v>72</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -5459,139 +6169,156 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="19" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E21" s="5" t="s">
+    <row r="22" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="7" t="s">
+    <row r="23" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="B23" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>100</v>
-      </c>
     </row>
     <row r="24" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>73</v>
+      <c r="E24" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="25" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="7" t="s">
+    <row r="27" ht="46" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+    <row r="29" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5614,7 +6341,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5622,7 +6349,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5633,13 +6360,13 @@
         <v>32</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5647,13 +6374,13 @@
         <v>48</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -5661,200 +6388,200 @@
         <v>55</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -5887,7 +6614,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5896,7 +6623,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5905,228 +6632,228 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>165</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>178</v>
-      </c>
       <c r="C9" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -6160,7 +6887,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6168,7 +6895,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6176,41 +6903,41 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>37</v>
@@ -6218,13 +6945,13 @@
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>37</v>
@@ -6232,27 +6959,27 @@
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>37</v>
@@ -6260,69 +6987,69 @@
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>37</v>
@@ -6330,27 +7057,27 @@
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>37</v>
@@ -6358,21 +7085,21 @@
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -6380,7 +7107,7 @@
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
@@ -6415,7 +7142,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6424,7 +7151,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6433,78 +7160,78 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>269</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>37</v>
@@ -6513,15 +7240,15 @@
         <v>37</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>37</v>
@@ -6530,15 +7257,15 @@
         <v>37</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>281</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>277</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>37</v>
@@ -6547,15 +7274,15 @@
         <v>37</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>37</v>
@@ -6564,12 +7291,12 @@
         <v>37</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -6601,19 +7328,19 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>3</v>
@@ -6621,135 +7348,135 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B23" s="10"/>
     </row>
@@ -6778,217 +7505,217 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B9" s="10"/>
     </row>
     <row r="11" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B32" s="9"/>
     </row>
@@ -7019,164 +7746,164 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>388</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
